--- a/Arquivos_MNT/dados_acareacoes_MNT.xlsx
+++ b/Arquivos_MNT/dados_acareacoes_MNT.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,45 +466,92 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>3320056494667</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>(MNT INT) VINICIUS GOULART (MENDES P)))</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Fake Delivery</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>lorrane Marques Martins</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>+5527992582609</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Rua Evandro de Castro 28, Mendes Pimentel</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Capinha Capa de silicone Anti-impacto silicone Resistente A Choques Pokémon para Galaxy A03 A04 A04E A05 A05S A10 A10S A11 A12 A14 A15 A20 A30 A23 A32 A34 A35 A50 A51 A52 A54 A55 A71 A72 M23 M34 M52 M53 S20 S21 S22 S23 S24 FE ULTRA PLUS 4G*1</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>3.83</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2026-06-09 13:26:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>3320031492820</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>(MNT INT) GILCLEBER (CSP)</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Fake Delivery</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Sônia Maria Alves neto</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>+5533999025656</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Av 8 de Dezembro 922 Comércio esquina, Galiléia</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>[Camiseta Premium Algodão]JOJO Oversized Basica Masculina E Feminina(Unissex)100% Algodão Folgada Plus Size G1G2G3#F4150*1</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>11.17</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>2026-06-08 14:25:32</t>
         </is>

--- a/Arquivos_MNT/dados_acareacoes_MNT.xlsx
+++ b/Arquivos_MNT/dados_acareacoes_MNT.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,12 +466,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>3320056494667</t>
+          <t>3320051639440</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>(MNT INT) VINICIUS GOULART (MENDES P)))</t>
+          <t>(MNT INT) VINICIUS GOULART (MENDES P)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -481,39 +481,39 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>lorrane Marques Martins</t>
+          <t>Sergio Raimundo</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>+5527992582609</t>
+          <t>+5553398236448</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rua Evandro de Castro 28, Mendes Pimentel</t>
+          <t>Evandro de Castro 194 casa, Mendes Pimentel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Capinha Capa de silicone Anti-impacto silicone Resistente A Choques Pokémon para Galaxy A03 A04 A04E A05 A05S A10 A10S A11 A12 A14 A15 A20 A30 A23 A32 A34 A35 A50 A51 A52 A54 A55 A71 A72 M23 M34 M52 M53 S20 S21 S22 S23 S24 FE ULTRA PLUS 4G*1</t>
+          <t>Perfume Masculino Intense Men Pour Homme 100ml - Beleza Que Só*1</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>3.83</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-06-09 13:26:31</t>
+          <t>2026-08-07 11:26:03</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3320031492820</t>
+          <t>3320094754092</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -528,32 +528,220 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Sônia Maria Alves neto</t>
+          <t>Leticia Luciano</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>+5533999025656</t>
+          <t>+5533998418234</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Av 8 de Dezembro 922 Comércio esquina, Galiléia</t>
+          <t>Rua São Tomé 662 Apartamento, Galiléia</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>[Camiseta Premium Algodão]JOJO Oversized Basica Masculina E Feminina(Unissex)100% Algodão Folgada Plus Size G1G2G3#F4150*1</t>
+          <t>HM MODA Short alfaiataria simples feminina com bolso frontal , de ziper por lado*1</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>11.17</t>
+          <t>8.48</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-06-08 14:25:32</t>
+          <t>2026-08-07 11:23:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>3320084759899</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>(MNT INT) THAMIRES (RESPLENDOR)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Fake Delivery</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>juninhoxavier880</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>+5533998650281</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Custódio Fernandes 203, Resplendor</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Kit 12, 10, 8, 5 ou 3 Cuecas Boxer Infantil 3 a 8 anos Microfibra Premium Menino*1</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>14.99</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2026-08-07 11:22:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>3320093757519</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>(MNT INT) GILCLEBER (CSP)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Fake Delivery</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Wagner José Pereira José Pereira</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>+5533998729278</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>rua Dorival machado 263 casa, Galiléia</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Livro Escola Divertida Especial - Alfabeto*1</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>15.47</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2026-08-07 11:21:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>3320000764121</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>(MNT INT) GILCLEBER (CSP)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Fake Delivery</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>gil</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>+5533998182915</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Centro 443 Casa, São Geraldo do Baixio</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Tamanco Modal Feminino Macio Ortopédico Anatômico*1</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>33.9</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2026-08-07 11:21:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>3320023746051</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>(MNT INT) ARILSON (S. J. DIVINO)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Fake Delivery</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Ana Lúcia De Souza</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>+5553399261141</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Avenida Minas Gerais 276 Mercearia Dutra, São José do Divino</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Axiu Corretivo Líquido com pincel Efeito Matte Para Olheiras e Manchas Alta Cobertura Multicover ak5 tendência*1</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0.93</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2026-08-06 09:39:54</t>
         </is>
       </c>
     </row>
